--- a/artfynd/A 43738-2020 artfynd.xlsx
+++ b/artfynd/A 43738-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43738-2020 artfynd.xlsx
+++ b/artfynd/A 43738-2020 artfynd.xlsx
@@ -1798,11 +1798,11 @@
         <v>98309843</v>
       </c>
       <c r="B12" t="n">
-        <v>94838</v>
+        <v>96929</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dialog hos validator</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>757009.5448187832</v>
+        <v>757009</v>
       </c>
       <c r="R12" t="n">
-        <v>7351585.374276507</v>
+        <v>7351585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1868,9 @@
           <t>2021-07-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 43738-2020 artfynd.xlsx
+++ b/artfynd/A 43738-2020 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>98309843</v>
       </c>
       <c r="B12" t="n">
-        <v>96929</v>
+        <v>96945</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 43738-2020 artfynd.xlsx
+++ b/artfynd/A 43738-2020 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>98309843</v>
       </c>
       <c r="B12" t="n">
-        <v>96945</v>
+        <v>96947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 43738-2020 artfynd.xlsx
+++ b/artfynd/A 43738-2020 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>98309843</v>
       </c>
       <c r="B12" t="n">
-        <v>96947</v>
+        <v>96707</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
